--- a/sheets/조재수대금교본/검수/타령.xlsx
+++ b/sheets/조재수대금교본/검수/타령.xlsx
@@ -8839,7 +8839,7 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∽汰㳞
+          <t xml:space="preserve">汰㳞
 –</t>
         </is>
       </c>
@@ -8858,7 +8858,7 @@
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="O3" s="22"/>
@@ -8876,7 +8876,7 @@
       <c r="S3" s="22"/>
       <c r="T3" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="U3" s="24"/>
@@ -8885,15 +8885,13 @@
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C4" s="25"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E4" s="25"/>
@@ -8903,15 +8901,13 @@
       <c r="I4" s="25"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K4" s="25"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M4" s="25"/>
@@ -8919,8 +8915,7 @@
       <c r="O4" s="25"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-⌝</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q4" s="25"/>
@@ -8933,8 +8928,7 @@
       <c r="S4" s="25"/>
       <c r="T4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U4" s="25"/>
@@ -8949,22 +8943,13 @@
       <c r="C5" s="26"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-ﾉ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="E5" s="26"/>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="F5" s="21"/>
       <c r="G5" s="26"/>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H5" s="21"/>
       <c r="I5" s="26"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
@@ -8981,7 +8966,7 @@
       <c r="M5" s="26"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ʒ</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="O5" s="26"/>
@@ -8993,8 +8978,7 @@
       <c r="Q5" s="26"/>
       <c r="R5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="S5" s="26"/>
@@ -9025,11 +9009,7 @@
         </is>
       </c>
       <c r="G6" s="22"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H6" s="21"/>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
@@ -9039,7 +9019,7 @@
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="M6" s="22"/>
@@ -9063,8 +9043,7 @@
       <c r="S6" s="22"/>
       <c r="T6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-ﾉ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="U6" s="22"/>
@@ -9075,22 +9054,19 @@
       <c r="C7" s="25"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-⌝</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G7" s="25"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-⌝</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="25"/>
@@ -9103,29 +9079,28 @@
       <c r="K7" s="25"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–ﾉ
-汏∽</t>
+          <t xml:space="preserve">–
+汏</t>
         </is>
       </c>
       <c r="M7" s="25"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–ﾉ
-汰∽</t>
+          <t xml:space="preserve">–
+汰</t>
         </is>
       </c>
       <c r="O7" s="25"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–ﾉ
-汏∽</t>
+          <t xml:space="preserve">–
+汏</t>
         </is>
       </c>
       <c r="Q7" s="25"/>
       <c r="R7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S7" s="25"/>
@@ -9140,37 +9115,32 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-ﾉ
-–太∽</t>
+–太</t>
         </is>
       </c>
       <c r="E8" s="26"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-ﾉ</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="G8" s="26"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I8" s="26"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="K8" s="26"/>
@@ -9188,22 +9158,20 @@
       <c r="O8" s="26"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="Q8" s="26"/>
       <c r="R8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㳞
-–汰∽</t>
+–汰</t>
         </is>
       </c>
       <c r="S8" s="26"/>
       <c r="T8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ
-∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="U8" s="26"/>
@@ -9242,19 +9210,19 @@
       <c r="K9" s="22"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∧</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∧</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="O9" s="22"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∧</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="Q9" s="22"/>
@@ -9275,8 +9243,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C10" s="25"/>
@@ -9289,43 +9256,37 @@
       <c r="E10" s="25"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G10" s="25"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I10" s="25"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K10" s="25"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M10" s="25"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O10" s="25"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q10" s="25"/>
@@ -9338,8 +9299,7 @@
       <c r="S10" s="25"/>
       <c r="T10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U10" s="25"/>
@@ -9355,14 +9315,14 @@
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林∼
-–ㄴ</t>
+–</t>
         </is>
       </c>
       <c r="E11" s="26"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-–ㄴ</t>
+–</t>
         </is>
       </c>
       <c r="G11" s="26"/>
@@ -9402,15 +9362,14 @@
       <c r="Q11" s="26"/>
       <c r="R11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="S11" s="26"/>
       <c r="T11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㳞
-–汰∽</t>
+–汰</t>
         </is>
       </c>
       <c r="U11" s="26"/>
@@ -9437,7 +9396,7 @@
       <c r="G12" s="22"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="I12" s="22"/>
@@ -9483,7 +9442,7 @@
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-太∽</t>
+太</t>
         </is>
       </c>
       <c r="C13" s="25"/>
@@ -9493,15 +9452,13 @@
       <c r="G13" s="25"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-⌝</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I13" s="25"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K13" s="25"/>
@@ -9509,8 +9466,7 @@
       <c r="M13" s="25"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O13" s="25"/>
@@ -9525,8 +9481,7 @@
       <c r="S13" s="25"/>
       <c r="T13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U13" s="25"/>
@@ -9535,45 +9490,33 @@
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="C14" s="26"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="26"/>
       <c r="F14" s="21"/>
       <c r="G14" s="26"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞汰
-–⌝
-‹</t>
+–</t>
         </is>
       </c>
       <c r="I14" s="26"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="K14" s="26"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="26"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="O14" s="26"/>
@@ -9582,14 +9525,14 @@
       <c r="R14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="S14" s="26"/>
       <c r="T14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林
-–ㄴ∼</t>
+–∼</t>
         </is>
       </c>
       <c r="U14" s="26"/>
@@ -9728,7 +9671,7 @@
       <c r="S20" s="22"/>
       <c r="T20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="U20" s="22"/>
@@ -9783,8 +9726,7 @@
       <c r="S22" s="26"/>
       <c r="T22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="U22" s="26"/>
@@ -9838,8 +9780,7 @@
       <c r="S24" s="25"/>
       <c r="T24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U24" s="25"/>
@@ -9866,7 +9807,7 @@
       <c r="S25" s="26"/>
       <c r="T25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南⌝
+          <t xml:space="preserve">南
 南</t>
         </is>
       </c>
@@ -9922,7 +9863,7 @@
       <c r="T27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-太∽</t>
+太</t>
         </is>
       </c>
       <c r="U27" s="25"/>
@@ -9949,8 +9890,7 @@
       <c r="S28" s="26"/>
       <c r="T28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="U28" s="26"/>
@@ -10006,15 +9946,11 @@
         </is>
       </c>
       <c r="G31" s="22"/>
-      <c r="H31" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ʊㄱ</t>
-        </is>
-      </c>
+      <c r="H31" s="21"/>
       <c r="I31" s="22"/>
       <c r="J31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∧
+          <t xml:space="preserve">湳
 –</t>
         </is>
       </c>
@@ -10027,7 +9963,7 @@
       <c r="M31" s="22"/>
       <c r="N31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="O31" s="22"/>
@@ -10058,8 +9994,7 @@
       <c r="E32" s="25"/>
       <c r="F32" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G32" s="25"/>
@@ -10073,15 +10008,14 @@
       <c r="O32" s="25"/>
       <c r="P32" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–ﾉ
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
       <c r="Q32" s="25"/>
       <c r="R32" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S32" s="25"/>
@@ -10095,12 +10029,7 @@
     </row>
     <row r="33" ht="106.4" customHeight="true">
       <c r="A33" s="0"/>
-      <c r="B33" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="B33" s="21"/>
       <c r="C33" s="26"/>
       <c r="D33" s="21"/>
       <c r="E33" s="26"/>
@@ -10158,11 +10087,7 @@
         </is>
       </c>
       <c r="G34" s="22"/>
-      <c r="H34" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">∧</t>
-        </is>
-      </c>
+      <c r="H34" s="21"/>
       <c r="I34" s="22"/>
       <c r="J34" s="21" t="inlineStr">
         <is>
@@ -10180,8 +10105,7 @@
       <c r="O34" s="22"/>
       <c r="P34" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-ﾉ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="Q34" s="22"/>
@@ -10193,7 +10117,7 @@
       <c r="S34" s="22"/>
       <c r="T34" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="U34" s="22"/>
@@ -10202,15 +10126,14 @@
       <c r="A35" s="0"/>
       <c r="B35" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-⌝</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C35" s="25"/>
       <c r="D35" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰∽</t>
+汰</t>
         </is>
       </c>
       <c r="E35" s="25"/>
@@ -10223,8 +10146,7 @@
       <c r="G35" s="25"/>
       <c r="H35" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I35" s="25"/>
@@ -10240,11 +10162,7 @@
         </is>
       </c>
       <c r="Q35" s="25"/>
-      <c r="R35" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="R35" s="21"/>
       <c r="S35" s="25"/>
       <c r="T35" s="21" t="inlineStr">
         <is>
@@ -10258,36 +10176,31 @@
       <c r="A36" s="0"/>
       <c r="B36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-ﾉ</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="C36" s="26"/>
       <c r="D36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="E36" s="26"/>
       <c r="F36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="G36" s="26"/>
       <c r="H36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-‹</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="I36" s="26"/>
       <c r="J36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-‹</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="K36" s="26"/>
@@ -10301,7 +10214,7 @@
       <c r="O36" s="26"/>
       <c r="P36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="Q36" s="26"/>
@@ -10313,8 +10226,7 @@
       <c r="S36" s="26"/>
       <c r="T36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="U36" s="26"/>
@@ -10389,36 +10301,31 @@
       <c r="C38" s="25"/>
       <c r="D38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E38" s="25"/>
       <c r="F38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G38" s="25"/>
       <c r="H38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I38" s="25"/>
       <c r="J38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K38" s="25"/>
       <c r="L38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M38" s="25"/>
@@ -10426,22 +10333,19 @@
       <c r="O38" s="25"/>
       <c r="P38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q38" s="25"/>
       <c r="R38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-∧</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S38" s="25"/>
       <c r="T38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U38" s="25"/>
@@ -10450,8 +10354,7 @@
       <c r="A39" s="0"/>
       <c r="B39" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-ﾉ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="C39" s="26"/>
@@ -10501,7 +10404,7 @@
       <c r="R39" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="S39" s="26"/>
@@ -10523,7 +10426,7 @@
       <c r="C40" s="22"/>
       <c r="D40" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E40" s="22"/>
@@ -10582,36 +10485,31 @@
       <c r="C41" s="25"/>
       <c r="D41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-⌝</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E41" s="25"/>
       <c r="F41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G41" s="25"/>
       <c r="H41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I41" s="25"/>
       <c r="J41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K41" s="25"/>
       <c r="L41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M41" s="25"/>
@@ -10619,15 +10517,13 @@
       <c r="O41" s="25"/>
       <c r="P41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q41" s="25"/>
       <c r="R41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S41" s="25"/>
@@ -10640,73 +10536,56 @@
     </row>
     <row r="42" ht="106.4" customHeight="true">
       <c r="A42" s="0"/>
-      <c r="B42" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B42" s="21"/>
       <c r="C42" s="26"/>
       <c r="D42" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞汰
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="E42" s="26"/>
       <c r="F42" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G42" s="26"/>
       <c r="H42" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="I42" s="26"/>
       <c r="J42" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="K42" s="26"/>
       <c r="L42" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="M42" s="26"/>
-      <c r="N42" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N42" s="21"/>
       <c r="O42" s="26"/>
       <c r="P42" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="Q42" s="26"/>
       <c r="R42" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳∼
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="S42" s="26"/>
-      <c r="T42" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T42" s="21"/>
       <c r="U42" s="26"/>
     </row>
     <row r="43" ht="6.0" customHeight="true">
@@ -10761,7 +10640,7 @@
       <c r="S45" s="22"/>
       <c r="T45" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄱ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="U45" s="22"/>
@@ -10861,8 +10740,7 @@
       <c r="S49" s="25"/>
       <c r="T49" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-⌝</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U49" s="25"/>
@@ -10889,9 +10767,7 @@
       <c r="S50" s="26"/>
       <c r="T50" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-ﾉ
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="U50" s="26"/>
@@ -11000,7 +10876,7 @@
       <c r="S54" s="22"/>
       <c r="T54" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
+          <t xml:space="preserve">潢
 –</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/타령.xlsx
+++ b/sheets/조재수대금교본/검수/타령.xlsx
@@ -8839,7 +8839,7 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰㳞
+          <t xml:space="preserve">∽汰㳞
 –</t>
         </is>
       </c>
@@ -8858,7 +8858,7 @@
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="O3" s="22"/>
@@ -8876,7 +8876,7 @@
       <c r="S3" s="22"/>
       <c r="T3" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∽</t>
         </is>
       </c>
       <c r="U3" s="24"/>
@@ -8885,13 +8885,15 @@
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="C4" s="25"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="E4" s="25"/>
@@ -8901,13 +8903,15 @@
       <c r="I4" s="25"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="K4" s="25"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="M4" s="25"/>
@@ -8915,7 +8919,8 @@
       <c r="O4" s="25"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+⌝</t>
         </is>
       </c>
       <c r="Q4" s="25"/>
@@ -8928,7 +8933,8 @@
       <c r="S4" s="25"/>
       <c r="T4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="U4" s="25"/>
@@ -8943,11 +8949,16 @@
       <c r="C5" s="26"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南
+ﾉ</t>
         </is>
       </c>
       <c r="E5" s="26"/>
-      <c r="F5" s="21"/>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="G5" s="26"/>
       <c r="H5" s="21"/>
       <c r="I5" s="26"/>
@@ -8966,7 +8977,7 @@
       <c r="M5" s="26"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋ʒ</t>
         </is>
       </c>
       <c r="O5" s="26"/>
@@ -9009,7 +9020,11 @@
         </is>
       </c>
       <c r="G6" s="22"/>
-      <c r="H6" s="21"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
@@ -9019,7 +9034,7 @@
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="M6" s="22"/>
@@ -9043,7 +9058,8 @@
       <c r="S6" s="22"/>
       <c r="T6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∧
+ﾉ</t>
         </is>
       </c>
       <c r="U6" s="22"/>
@@ -9054,19 +9070,22 @@
       <c r="C7" s="25"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+⌝</t>
         </is>
       </c>
       <c r="G7" s="25"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+⌝</t>
         </is>
       </c>
       <c r="I7" s="25"/>
@@ -9079,28 +9098,29 @@
       <c r="K7" s="25"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-汏</t>
+          <t xml:space="preserve">–ﾉ
+汏∽</t>
         </is>
       </c>
       <c r="M7" s="25"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-汰</t>
+          <t xml:space="preserve">–ﾉ
+汰∽</t>
         </is>
       </c>
       <c r="O7" s="25"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-汏</t>
+          <t xml:space="preserve">–ﾉ
+汏∽</t>
         </is>
       </c>
       <c r="Q7" s="25"/>
       <c r="R7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="S7" s="25"/>
@@ -9122,13 +9142,15 @@
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-–太</t>
+ﾉ
+–太∽</t>
         </is>
       </c>
       <c r="E8" s="26"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲
+ﾉ</t>
         </is>
       </c>
       <c r="G8" s="26"/>
@@ -9165,13 +9187,14 @@
       <c r="R8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㳞
-–汰</t>
+–汰∽</t>
         </is>
       </c>
       <c r="S8" s="26"/>
       <c r="T8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ
+∽</t>
         </is>
       </c>
       <c r="U8" s="26"/>
@@ -9210,19 +9233,19 @@
       <c r="K9" s="22"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋∧</t>
         </is>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋∧</t>
         </is>
       </c>
       <c r="O9" s="22"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋∧</t>
         </is>
       </c>
       <c r="Q9" s="22"/>
@@ -9243,7 +9266,8 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="C10" s="25"/>
@@ -9256,37 +9280,43 @@
       <c r="E10" s="25"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="G10" s="25"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="I10" s="25"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="K10" s="25"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="M10" s="25"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="O10" s="25"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="Q10" s="25"/>
@@ -9299,7 +9329,8 @@
       <c r="S10" s="25"/>
       <c r="T10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="U10" s="25"/>
@@ -9315,14 +9346,14 @@
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林∼
-–</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="E11" s="26"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-–</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="G11" s="26"/>
@@ -9369,7 +9400,7 @@
       <c r="T11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㳞
-–汰</t>
+–汰∽</t>
         </is>
       </c>
       <c r="U11" s="26"/>
@@ -9396,7 +9427,7 @@
       <c r="G12" s="22"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="I12" s="22"/>
@@ -9442,7 +9473,7 @@
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-太</t>
+太∽</t>
         </is>
       </c>
       <c r="C13" s="25"/>
@@ -9452,13 +9483,15 @@
       <c r="G13" s="25"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+⌝</t>
         </is>
       </c>
       <c r="I13" s="25"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="K13" s="25"/>
@@ -9466,7 +9499,8 @@
       <c r="M13" s="25"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="O13" s="25"/>
@@ -9481,7 +9515,8 @@
       <c r="S13" s="25"/>
       <c r="T13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="U13" s="25"/>
@@ -9501,7 +9536,7 @@
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞汰
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="I14" s="26"/>
@@ -9525,14 +9560,14 @@
       <c r="R14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="S14" s="26"/>
       <c r="T14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林
-–∼</t>
+–ㄴ∼</t>
         </is>
       </c>
       <c r="U14" s="26"/>
@@ -9671,7 +9706,7 @@
       <c r="S20" s="22"/>
       <c r="T20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="U20" s="22"/>
@@ -9780,7 +9815,8 @@
       <c r="S24" s="25"/>
       <c r="T24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="U24" s="25"/>
@@ -9807,7 +9843,7 @@
       <c r="S25" s="26"/>
       <c r="T25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南⌝
 南</t>
         </is>
       </c>
@@ -9863,7 +9899,7 @@
       <c r="T27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-太</t>
+太∽</t>
         </is>
       </c>
       <c r="U27" s="25"/>
@@ -9946,11 +9982,15 @@
         </is>
       </c>
       <c r="G31" s="22"/>
-      <c r="H31" s="21"/>
+      <c r="H31" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ʊㄱ</t>
+        </is>
+      </c>
       <c r="I31" s="22"/>
       <c r="J31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
+          <t xml:space="preserve">湳∧
 –</t>
         </is>
       </c>
@@ -9963,7 +10003,7 @@
       <c r="M31" s="22"/>
       <c r="N31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="O31" s="22"/>
@@ -9994,7 +10034,8 @@
       <c r="E32" s="25"/>
       <c r="F32" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="G32" s="25"/>
@@ -10008,14 +10049,15 @@
       <c r="O32" s="25"/>
       <c r="P32" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
+          <t xml:space="preserve">–ﾉ
 汰</t>
         </is>
       </c>
       <c r="Q32" s="25"/>
       <c r="R32" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="S32" s="25"/>
@@ -10029,7 +10071,11 @@
     </row>
     <row r="33" ht="106.4" customHeight="true">
       <c r="A33" s="0"/>
-      <c r="B33" s="21"/>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="C33" s="26"/>
       <c r="D33" s="21"/>
       <c r="E33" s="26"/>
@@ -10087,7 +10133,11 @@
         </is>
       </c>
       <c r="G34" s="22"/>
-      <c r="H34" s="21"/>
+      <c r="H34" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">∧</t>
+        </is>
+      </c>
       <c r="I34" s="22"/>
       <c r="J34" s="21" t="inlineStr">
         <is>
@@ -10105,7 +10155,8 @@
       <c r="O34" s="22"/>
       <c r="P34" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∧
+ﾉ</t>
         </is>
       </c>
       <c r="Q34" s="22"/>
@@ -10117,7 +10168,7 @@
       <c r="S34" s="22"/>
       <c r="T34" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="U34" s="22"/>
@@ -10126,14 +10177,15 @@
       <c r="A35" s="0"/>
       <c r="B35" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+⌝</t>
         </is>
       </c>
       <c r="C35" s="25"/>
       <c r="D35" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰</t>
+汰∽</t>
         </is>
       </c>
       <c r="E35" s="25"/>
@@ -10146,7 +10198,8 @@
       <c r="G35" s="25"/>
       <c r="H35" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="I35" s="25"/>
@@ -10162,7 +10215,11 @@
         </is>
       </c>
       <c r="Q35" s="25"/>
-      <c r="R35" s="21"/>
+      <c r="R35" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="S35" s="25"/>
       <c r="T35" s="21" t="inlineStr">
         <is>
@@ -10176,7 +10233,8 @@
       <c r="A36" s="0"/>
       <c r="B36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲
+ﾉ</t>
         </is>
       </c>
       <c r="C36" s="26"/>
@@ -10214,7 +10272,7 @@
       <c r="O36" s="26"/>
       <c r="P36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="Q36" s="26"/>
@@ -10301,31 +10359,36 @@
       <c r="C38" s="25"/>
       <c r="D38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="E38" s="25"/>
       <c r="F38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="G38" s="25"/>
       <c r="H38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="I38" s="25"/>
       <c r="J38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="K38" s="25"/>
       <c r="L38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="M38" s="25"/>
@@ -10333,19 +10396,22 @@
       <c r="O38" s="25"/>
       <c r="P38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="Q38" s="25"/>
       <c r="R38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+∧</t>
         </is>
       </c>
       <c r="S38" s="25"/>
       <c r="T38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="U38" s="25"/>
@@ -10354,7 +10420,8 @@
       <c r="A39" s="0"/>
       <c r="B39" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南
+ﾉ</t>
         </is>
       </c>
       <c r="C39" s="26"/>
@@ -10404,7 +10471,7 @@
       <c r="R39" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="S39" s="26"/>
@@ -10426,7 +10493,7 @@
       <c r="C40" s="22"/>
       <c r="D40" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="E40" s="22"/>
@@ -10485,31 +10552,36 @@
       <c r="C41" s="25"/>
       <c r="D41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+⌝</t>
         </is>
       </c>
       <c r="E41" s="25"/>
       <c r="F41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="G41" s="25"/>
       <c r="H41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="I41" s="25"/>
       <c r="J41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="K41" s="25"/>
       <c r="L41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="M41" s="25"/>
@@ -10517,13 +10589,15 @@
       <c r="O41" s="25"/>
       <c r="P41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="Q41" s="25"/>
       <c r="R41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="S41" s="25"/>
@@ -10541,7 +10615,7 @@
       <c r="D42" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞汰
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="E42" s="26"/>
@@ -10581,7 +10655,7 @@
       <c r="R42" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳∼
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="S42" s="26"/>
@@ -10640,7 +10714,7 @@
       <c r="S45" s="22"/>
       <c r="T45" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄱ</t>
         </is>
       </c>
       <c r="U45" s="22"/>
@@ -10740,7 +10814,8 @@
       <c r="S49" s="25"/>
       <c r="T49" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+⌝</t>
         </is>
       </c>
       <c r="U49" s="25"/>
@@ -10767,7 +10842,8 @@
       <c r="S50" s="26"/>
       <c r="T50" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲
+ﾉ</t>
         </is>
       </c>
       <c r="U50" s="26"/>
@@ -10876,7 +10952,7 @@
       <c r="S54" s="22"/>
       <c r="T54" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">潢ʒ
 –</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/타령.xlsx
+++ b/sheets/조재수대금교본/검수/타령.xlsx
@@ -8765,32 +8765,32 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="13.46" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="13.46" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="71.43" customHeight="true">
+    <row r="2" ht="93.02" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="106.4" customHeight="true">
+    <row r="3" ht="138.71" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="U3" s="24"/>
     </row>
-    <row r="4" ht="106.4" customHeight="true">
+    <row r="4" ht="138.71" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
       </c>
       <c r="U4" s="25"/>
     </row>
-    <row r="5" ht="106.4" customHeight="true">
+    <row r="5" ht="138.71" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="U5" s="26"/>
     </row>
-    <row r="6" ht="106.4" customHeight="true">
+    <row r="6" ht="138.71" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="106.4" customHeight="true">
+    <row r="7" ht="138.71" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="25"/>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="U7" s="25"/>
     </row>
-    <row r="8" ht="106.4" customHeight="true">
+    <row r="8" ht="138.71" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
       </c>
       <c r="U8" s="26"/>
     </row>
-    <row r="9" ht="106.4" customHeight="true">
+    <row r="9" ht="138.71" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="106.4" customHeight="true">
+    <row r="10" ht="138.71" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="U10" s="25"/>
     </row>
-    <row r="11" ht="106.4" customHeight="true">
+    <row r="11" ht="138.71" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="U11" s="26"/>
     </row>
-    <row r="12" ht="106.4" customHeight="true">
+    <row r="12" ht="138.71" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="106.4" customHeight="true">
+    <row r="13" ht="138.71" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="U13" s="25"/>
     </row>
-    <row r="14" ht="106.4" customHeight="true">
+    <row r="14" ht="138.71" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
     <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="71.43" customHeight="true">
+    <row r="16" ht="93.02" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="106.4" customHeight="true">
+    <row r="17" ht="138.71" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="U17" s="22"/>
     </row>
-    <row r="18" ht="106.4" customHeight="true">
+    <row r="18" ht="138.71" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="25"/>
@@ -9657,7 +9657,7 @@
       </c>
       <c r="U18" s="25"/>
     </row>
-    <row r="19" ht="106.4" customHeight="true">
+    <row r="19" ht="138.71" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="26"/>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="U19" s="26"/>
     </row>
-    <row r="20" ht="106.4" customHeight="true">
+    <row r="20" ht="138.71" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="U20" s="22"/>
     </row>
-    <row r="21" ht="106.4" customHeight="true">
+    <row r="21" ht="138.71" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="25"/>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="U21" s="25"/>
     </row>
-    <row r="22" ht="106.4" customHeight="true">
+    <row r="22" ht="138.71" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="26"/>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="U22" s="26"/>
     </row>
-    <row r="23" ht="106.4" customHeight="true">
+    <row r="23" ht="138.71" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="U23" s="22"/>
     </row>
-    <row r="24" ht="106.4" customHeight="true">
+    <row r="24" ht="138.71" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="25"/>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="U24" s="25"/>
     </row>
-    <row r="25" ht="106.4" customHeight="true">
+    <row r="25" ht="138.71" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="26"/>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="U25" s="26"/>
     </row>
-    <row r="26" ht="106.4" customHeight="true">
+    <row r="26" ht="138.71" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="U26" s="22"/>
     </row>
-    <row r="27" ht="106.4" customHeight="true">
+    <row r="27" ht="138.71" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="25"/>
@@ -9904,7 +9904,7 @@
       </c>
       <c r="U27" s="25"/>
     </row>
-    <row r="28" ht="106.4" customHeight="true">
+    <row r="28" ht="138.71" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="26"/>
@@ -9934,7 +9934,7 @@
     <row r="29" ht="6.0" customHeight="true">
       <c r="A29" s="0"/>
     </row>
-    <row r="30" ht="71.43" customHeight="true">
+    <row r="30" ht="93.02" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="20" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
       <c r="T30" s="20"/>
       <c r="U30" s="20"/>
     </row>
-    <row r="31" ht="106.4" customHeight="true">
+    <row r="31" ht="138.71" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="U31" s="22"/>
     </row>
-    <row r="32" ht="106.4" customHeight="true">
+    <row r="32" ht="138.71" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="25"/>
@@ -10069,7 +10069,7 @@
       </c>
       <c r="U32" s="25"/>
     </row>
-    <row r="33" ht="106.4" customHeight="true">
+    <row r="33" ht="138.71" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
       </c>
       <c r="U33" s="26"/>
     </row>
-    <row r="34" ht="106.4" customHeight="true">
+    <row r="34" ht="138.71" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="U34" s="22"/>
     </row>
-    <row r="35" ht="106.4" customHeight="true">
+    <row r="35" ht="138.71" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
       </c>
       <c r="U35" s="25"/>
     </row>
-    <row r="36" ht="106.4" customHeight="true">
+    <row r="36" ht="138.71" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="U36" s="26"/>
     </row>
-    <row r="37" ht="106.4" customHeight="true">
+    <row r="37" ht="138.71" customHeight="true">
       <c r="A37" s="0"/>
       <c r="B37" s="21" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="U37" s="22"/>
     </row>
-    <row r="38" ht="106.4" customHeight="true">
+    <row r="38" ht="138.71" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="21" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
       </c>
       <c r="U38" s="25"/>
     </row>
-    <row r="39" ht="106.4" customHeight="true">
+    <row r="39" ht="138.71" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="21" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
       </c>
       <c r="U39" s="26"/>
     </row>
-    <row r="40" ht="106.4" customHeight="true">
+    <row r="40" ht="138.71" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="21" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="U40" s="22"/>
     </row>
-    <row r="41" ht="106.4" customHeight="true">
+    <row r="41" ht="138.71" customHeight="true">
       <c r="A41" s="0"/>
       <c r="B41" s="21"/>
       <c r="C41" s="25"/>
@@ -10608,7 +10608,7 @@
       </c>
       <c r="U41" s="25"/>
     </row>
-    <row r="42" ht="106.4" customHeight="true">
+    <row r="42" ht="138.71" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="21"/>
       <c r="C42" s="26"/>
@@ -10665,7 +10665,7 @@
     <row r="43" ht="6.0" customHeight="true">
       <c r="A43" s="0"/>
     </row>
-    <row r="44" ht="71.43" customHeight="true">
+    <row r="44" ht="93.02" customHeight="true">
       <c r="A44" s="0"/>
       <c r="B44" s="20" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
       <c r="T44" s="20"/>
       <c r="U44" s="20"/>
     </row>
-    <row r="45" ht="106.4" customHeight="true">
+    <row r="45" ht="138.71" customHeight="true">
       <c r="A45" s="0"/>
       <c r="B45" s="21"/>
       <c r="C45" s="22"/>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="U45" s="22"/>
     </row>
-    <row r="46" ht="106.4" customHeight="true">
+    <row r="46" ht="138.71" customHeight="true">
       <c r="A46" s="0"/>
       <c r="B46" s="21"/>
       <c r="C46" s="25"/>
@@ -10742,7 +10742,7 @@
       <c r="T46" s="21"/>
       <c r="U46" s="25"/>
     </row>
-    <row r="47" ht="106.4" customHeight="true">
+    <row r="47" ht="138.71" customHeight="true">
       <c r="A47" s="0"/>
       <c r="B47" s="21"/>
       <c r="C47" s="26"/>
@@ -10765,7 +10765,7 @@
       <c r="T47" s="21"/>
       <c r="U47" s="26"/>
     </row>
-    <row r="48" ht="106.4" customHeight="true">
+    <row r="48" ht="138.71" customHeight="true">
       <c r="A48" s="0"/>
       <c r="B48" s="21"/>
       <c r="C48" s="22"/>
@@ -10792,7 +10792,7 @@
       </c>
       <c r="U48" s="22"/>
     </row>
-    <row r="49" ht="106.4" customHeight="true">
+    <row r="49" ht="138.71" customHeight="true">
       <c r="A49" s="0"/>
       <c r="B49" s="21"/>
       <c r="C49" s="25"/>
@@ -10820,7 +10820,7 @@
       </c>
       <c r="U49" s="25"/>
     </row>
-    <row r="50" ht="106.4" customHeight="true">
+    <row r="50" ht="138.71" customHeight="true">
       <c r="A50" s="0"/>
       <c r="B50" s="21"/>
       <c r="C50" s="26"/>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="U50" s="26"/>
     </row>
-    <row r="51" ht="106.4" customHeight="true">
+    <row r="51" ht="138.71" customHeight="true">
       <c r="A51" s="0"/>
       <c r="B51" s="21"/>
       <c r="C51" s="22"/>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="U51" s="22"/>
     </row>
-    <row r="52" ht="106.4" customHeight="true">
+    <row r="52" ht="138.71" customHeight="true">
       <c r="A52" s="0"/>
       <c r="B52" s="21"/>
       <c r="C52" s="25"/>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="U52" s="25"/>
     </row>
-    <row r="53" ht="106.4" customHeight="true">
+    <row r="53" ht="138.71" customHeight="true">
       <c r="A53" s="0"/>
       <c r="B53" s="21"/>
       <c r="C53" s="26"/>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="U53" s="26"/>
     </row>
-    <row r="54" ht="106.4" customHeight="true">
+    <row r="54" ht="138.71" customHeight="true">
       <c r="A54" s="0"/>
       <c r="B54" s="21"/>
       <c r="C54" s="22"/>
@@ -10958,7 +10958,7 @@
       </c>
       <c r="U54" s="22"/>
     </row>
-    <row r="55" ht="106.4" customHeight="true">
+    <row r="55" ht="138.71" customHeight="true">
       <c r="A55" s="0"/>
       <c r="B55" s="21"/>
       <c r="C55" s="25"/>
@@ -10981,7 +10981,7 @@
       <c r="T55" s="21"/>
       <c r="U55" s="25"/>
     </row>
-    <row r="56" ht="106.4" customHeight="true">
+    <row r="56" ht="138.71" customHeight="true">
       <c r="A56" s="0"/>
       <c r="B56" s="21"/>
       <c r="C56" s="26"/>
@@ -11018,7 +11018,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="43"/>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="14" max="16383" man="1"/>
     <brk id="28" max="16383" man="1"/>
